--- a/exports/BSE_full_report.xlsx
+++ b/exports/BSE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>229</v>
+        <v>217.5</v>
       </c>
       <c r="I2" t="n">
         <v>220.7303990750989</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>5.77</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="n">
         <v>0.84</v>
       </c>
       <c r="N2" t="n">
-        <v>4.38</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>231</v>
+        <v>241.5</v>
       </c>
       <c r="I3" t="n">
         <v>238.7785918306572</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.21</v>
+        <v>-11.03</v>
       </c>
       <c r="L3" t="n">
-        <v>6.44</v>
+        <v>11.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.37</v>
       </c>
       <c r="N3" t="n">
-        <v>4.52</v>
+        <v>5.63</v>
       </c>
       <c r="O3" t="n">
         <v>-4.8</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>11.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="I4" t="n">
         <v>230.4974993986133</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.62</v>
+        <v>-4.76</v>
       </c>
       <c r="L4" t="n">
         <v>7.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.58</v>
+        <v>5.21</v>
       </c>
       <c r="N4" t="n">
         <v>5.93</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.43</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.55208333334</v>
+        <v>44629.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>236</v>
+        <v>242.5</v>
       </c>
       <c r="I5" t="n">
         <v>237.2078233321408</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.61</v>
+        <v>-5.43</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7</v>
+        <v>5.43</v>
       </c>
       <c r="M5" t="n">
         <v>2.47</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>292.5</v>
+        <v>283.5</v>
       </c>
       <c r="I6" t="n">
         <v>286.313218785866</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>20.62</v>
+        <v>16.91</v>
       </c>
       <c r="L6" t="n">
         <v>2.06</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.77</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>289.5</v>
+        <v>306</v>
       </c>
       <c r="I7" t="n">
         <v>292.6384937857544</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.12</v>
+        <v>-7.94</v>
       </c>
       <c r="L7" t="n">
-        <v>4.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>10.2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>280.5</v>
+        <v>272</v>
       </c>
       <c r="I8" t="n">
         <v>277.694795993944</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.33</v>
+        <v>-11.11</v>
       </c>
       <c r="L8" t="n">
-        <v>9.48</v>
+        <v>12.25</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5</v>
+        <v>3.03</v>
       </c>
       <c r="N8" t="n">
         <v>4.36</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.23</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>231.5</v>
+        <v>246.5</v>
       </c>
       <c r="I9" t="n">
         <v>242.5974706183368</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>14.89</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>2.02</v>
@@ -954,7 +1061,7 @@
         <v>2.91</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>9.07</v>
       </c>
       <c r="O9" t="n">
         <v>-1.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>12.44</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>238.5</v>
+        <v>230.5</v>
       </c>
       <c r="I10" t="n">
         <v>231.6676997304084</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.25</v>
+        <v>-6.49</v>
       </c>
       <c r="L10" t="n">
         <v>6.9</v>
       </c>
       <c r="M10" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>4.82</v>
       </c>
       <c r="O10" t="n">
         <v>9.07</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.09</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>203.5</v>
+        <v>209.5</v>
       </c>
       <c r="I11" t="n">
         <v>208.3715047078073</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>11.71</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>2.17</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44778.55208333334</v>
+        <v>44781.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I12" t="n">
         <v>220.7327459831248</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>5.97</v>
+        <v>3.58</v>
       </c>
       <c r="L12" t="n">
         <v>2.86</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>220</v>
+        <v>225.5</v>
       </c>
       <c r="I13" t="n">
         <v>220.847288002016</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.38</v>
+        <v>-3.92</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>4.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.63</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I14" t="n">
         <v>218.7770179772236</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.11</v>
+        <v>-3.33</v>
       </c>
       <c r="L14" t="n">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
         <v>1.77</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.29</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>196.5</v>
+        <v>203</v>
       </c>
       <c r="I15" t="n">
         <v>201.9339271238424</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38.375</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>9.859999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="L15" t="n">
         <v>2.52</v>
@@ -1296,7 +1475,7 @@
         <v>1.74</v>
       </c>
       <c r="N15" t="n">
-        <v>1.49</v>
+        <v>3.56</v>
       </c>
       <c r="O15" t="n">
         <v>-0.45</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.48</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>195.5</v>
+        <v>192</v>
       </c>
       <c r="I16" t="n">
         <v>195.2366685853781</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.69</v>
+        <v>-5.42</v>
       </c>
       <c r="L16" t="n">
-        <v>4.19</v>
+        <v>5.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.75</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>5.35</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>190.5</v>
+        <v>193.5</v>
       </c>
       <c r="I17" t="n">
         <v>193.008120091202</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
-        <v>0.78</v>
+        <v>-0.78</v>
       </c>
       <c r="L17" t="n">
         <v>4.17</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="N17" t="n">
         <v>2.88</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.52</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I18" t="n">
         <v>187.9435889937973</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.29</v>
+        <v>-3.36</v>
       </c>
       <c r="L18" t="n">
-        <v>2.58</v>
+        <v>3.88</v>
       </c>
       <c r="M18" t="n">
         <v>0.52</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.04</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44929.38541666666</v>
+        <v>44929.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="I19" t="n">
         <v>187.5401126119688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>1.07</v>
+        <v>-0.8</v>
       </c>
       <c r="L19" t="n">
         <v>2.14</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.01</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44942.55208333334</v>
+        <v>44943.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I20" t="n">
         <v>177.1648750133827</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.57</v>
+        <v>-6.1</v>
       </c>
       <c r="L20" t="n">
         <v>6.1</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>176</v>
+        <v>179.5</v>
       </c>
       <c r="I21" t="n">
         <v>179.413384291247</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="L21" t="n">
         <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>0.28</v>
+        <v>0.85</v>
       </c>
       <c r="N21" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
         <v>-0.5600000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>4.69</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44953.38541666666</v>
+        <v>44953.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>172.5</v>
+        <v>171</v>
       </c>
       <c r="I22" t="n">
         <v>171.0764582098616</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.9</v>
+        <v>-4.74</v>
       </c>
       <c r="L22" t="n">
-        <v>4.74</v>
+        <v>5.01</v>
       </c>
       <c r="M22" t="n">
         <v>-0</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>149.5</v>
+        <v>161</v>
       </c>
       <c r="I23" t="n">
         <v>153.1628818901315</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>12.57</v>
+        <v>5.85</v>
       </c>
       <c r="L23" t="n">
         <v>2.34</v>
@@ -1752,7 +2027,7 @@
         <v>2.38</v>
       </c>
       <c r="N23" t="n">
-        <v>3.69</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-3.12</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>9.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>150.5</v>
+        <v>147.5</v>
       </c>
       <c r="I24" t="n">
         <v>148.9453568230034</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.52</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>7.45</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>1.24</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="I25" t="n">
         <v>145.0648915746101</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>2.71</v>
+        <v>-1.36</v>
       </c>
       <c r="L25" t="n">
         <v>6.78</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.24</v>
+        <v>4.53</v>
       </c>
       <c r="O25" t="n">
         <v>-2.66</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>292.5</v>
+        <v>281.5</v>
       </c>
       <c r="I26" t="n">
         <v>284.0430916878145</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>133.1666666666667</v>
+        <v>135</v>
       </c>
       <c r="K26" t="n">
-        <v>95.65000000000001</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>3.34</v>
       </c>
       <c r="M26" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="N26" t="n">
-        <v>3.42</v>
+        <v>4.62</v>
       </c>
       <c r="O26" t="n">
         <v>4.53</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.09</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>299</v>
+        <v>306.5</v>
       </c>
       <c r="I27" t="n">
         <v>304.1245826813723</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.22</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>7.46</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>0.7</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.19</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="I28" t="n">
         <v>405.135265117109</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>34.75</v>
+        <v>31.48</v>
       </c>
       <c r="L28" t="n">
         <v>3.75</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>14.28</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>437.5</v>
+        <v>441</v>
       </c>
       <c r="I29" t="n">
         <v>440.8211779124405</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.56</v>
+        <v>-9.43</v>
       </c>
       <c r="L29" t="n">
-        <v>8.56</v>
+        <v>12.53</v>
       </c>
       <c r="M29" t="n">
         <v>3.26</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45251.38541666666</v>
+        <v>45251.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>725.5</v>
+        <v>718</v>
       </c>
       <c r="I30" t="n">
         <v>720.4486200652173</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>54</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>64.51000000000001</v>
+        <v>62.81</v>
       </c>
       <c r="L30" t="n">
         <v>5.33</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45258.38541666666</v>
+        <v>45258.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>766.5</v>
+        <v>789</v>
       </c>
       <c r="I31" t="n">
         <v>783.3989210144583</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.75</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>7.59</v>
+        <v>10.03</v>
       </c>
       <c r="M31" t="n">
         <v>3.03</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.45</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>770</v>
+        <v>754.5</v>
       </c>
       <c r="I32" t="n">
         <v>763.6391990858306</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.41</v>
+        <v>-4.37</v>
       </c>
       <c r="L32" t="n">
         <v>6.21</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.58</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>732.5</v>
+        <v>758.5</v>
       </c>
       <c r="I33" t="n">
         <v>750.3021772937366</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>2.92</v>
+        <v>-0.53</v>
       </c>
       <c r="L33" t="n">
         <v>4.11</v>
@@ -2322,7 +2717,7 @@
         <v>0.8</v>
       </c>
       <c r="N33" t="n">
-        <v>3.27</v>
+        <v>6.28</v>
       </c>
       <c r="O33" t="n">
         <v>-2.21</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>10.3</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>783.5</v>
+        <v>781</v>
       </c>
       <c r="I34" t="n">
         <v>781.891620556949</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="L34" t="n">
         <v>3.96</v>
       </c>
       <c r="M34" t="n">
-        <v>0.41</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>4.84</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45348.55208333334</v>
+        <v>45349.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>759.5</v>
+        <v>791.5</v>
       </c>
       <c r="I35" t="n">
         <v>787.0549745486493</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>2.75</v>
+        <v>-1.34</v>
       </c>
       <c r="L35" t="n">
         <v>1.73</v>
@@ -2436,7 +2855,7 @@
         <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>5.33</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45358.55208333334</v>
+        <v>45362.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>747.5</v>
+        <v>735</v>
       </c>
       <c r="I36" t="n">
         <v>737.8026692708912</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.56</v>
+        <v>-7.14</v>
       </c>
       <c r="L36" t="n">
-        <v>5.69</v>
+        <v>7.33</v>
       </c>
       <c r="M36" t="n">
         <v>0.39</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.52</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45371.55208333334</v>
+        <v>45372.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>678.5</v>
+        <v>733</v>
       </c>
       <c r="I37" t="n">
         <v>728.5307434697488</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>7.69</v>
+        <v>0.27</v>
       </c>
       <c r="L37" t="n">
         <v>2.93</v>
       </c>
       <c r="M37" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="N37" t="n">
-        <v>4.06</v>
+        <v>10.69</v>
       </c>
       <c r="O37" t="n">
         <v>-2.01</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>12.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1071.5</v>
+        <v>936.5</v>
       </c>
       <c r="I38" t="n">
         <v>969.0110809700461</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K38" t="n">
-        <v>46.18</v>
+        <v>27.76</v>
       </c>
       <c r="L38" t="n">
         <v>5.66</v>
       </c>
       <c r="M38" t="n">
-        <v>3.17</v>
+        <v>15.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.61</v>
+        <v>13.3</v>
       </c>
       <c r="O38" t="n">
         <v>10.69</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>13.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>896.5</v>
+        <v>911</v>
       </c>
       <c r="I39" t="n">
         <v>909.5812401126622</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>4.27</v>
+        <v>2.72</v>
       </c>
       <c r="L39" t="n">
         <v>3.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>4.07</v>
       </c>
       <c r="N39" t="n">
         <v>5.71</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>905</v>
+        <v>849.5</v>
       </c>
       <c r="I40" t="n">
         <v>850.0585259578693</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.66</v>
+        <v>-6.75</v>
       </c>
       <c r="L40" t="n">
-        <v>1.21</v>
+        <v>11.25</v>
       </c>
       <c r="M40" t="n">
-        <v>-0</v>
+        <v>0.55</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="O40" t="n">
         <v>0.95</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.37</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45496.55208333334</v>
+        <v>45497.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>746</v>
+        <v>804.5</v>
       </c>
       <c r="I41" t="n">
         <v>795.4346818563384</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>12.18</v>
+        <v>5.3</v>
       </c>
       <c r="L41" t="n">
         <v>9.01</v>
@@ -2778,7 +3269,7 @@
         <v>1.81</v>
       </c>
       <c r="N41" t="n">
-        <v>3.72</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>-5.69</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>12.89</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>855.5</v>
+        <v>794</v>
       </c>
       <c r="I42" t="n">
         <v>808.1960733310151</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>6.34</v>
+        <v>-1.31</v>
       </c>
       <c r="L42" t="n">
         <v>7.02</v>
       </c>
       <c r="M42" t="n">
-        <v>2.44</v>
+        <v>4.79</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>7.07</v>
       </c>
       <c r="O42" t="n">
         <v>8.109999999999999</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>12.12</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45511.55208333334</v>
+        <v>45512.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>800</v>
+        <v>867</v>
       </c>
       <c r="I43" t="n">
         <v>862.998087592892</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.76</v>
+        <v>-9.19</v>
       </c>
       <c r="L43" t="n">
-        <v>4.53</v>
+        <v>11.52</v>
       </c>
       <c r="M43" t="n">
-        <v>2.45</v>
+        <v>10.69</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>7.88</v>
       </c>
       <c r="O43" t="n">
         <v>-7.07</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.41</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1451.5</v>
+        <v>1375.5</v>
       </c>
       <c r="I44" t="n">
         <v>1419.088651209868</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K44" t="n">
-        <v>67.42</v>
+        <v>58.65</v>
       </c>
       <c r="L44" t="n">
         <v>2.94</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>16.84</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45601.38541666666</v>
+        <v>45601.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>1486.5</v>
+        <v>1534</v>
       </c>
       <c r="I45" t="n">
         <v>1531.622848658966</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.07</v>
+        <v>-11.52</v>
       </c>
       <c r="L45" t="n">
-        <v>10.51</v>
+        <v>12.07</v>
       </c>
       <c r="M45" t="n">
         <v>1.14</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>10.78</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45622.38541666666</v>
+        <v>45622.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1481.5</v>
+        <v>1476.5</v>
       </c>
       <c r="I46" t="n">
         <v>1479.332750898729</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.42</v>
+        <v>-3.75</v>
       </c>
       <c r="L46" t="n">
-        <v>3.62</v>
+        <v>4.56</v>
       </c>
       <c r="M46" t="n">
         <v>0.07000000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1528.5</v>
+        <v>1684.5</v>
       </c>
       <c r="I47" t="n">
         <v>1626.358872362263</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.52</v>
+        <v>-14.09</v>
       </c>
       <c r="L47" t="n">
-        <v>6.3</v>
+        <v>16.69</v>
       </c>
       <c r="M47" t="n">
         <v>0.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2.23</v>
+        <v>14</v>
       </c>
       <c r="O47" t="n">
         <v>-3.72</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>13.16</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45652.55208333334</v>
+        <v>45653.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1812.5</v>
+        <v>1773</v>
       </c>
       <c r="I48" t="n">
         <v>1792.608109451433</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>7.6</v>
+        <v>5.25</v>
       </c>
       <c r="L48" t="n">
         <v>9.140000000000001</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1812</v>
+        <v>1924.5</v>
       </c>
       <c r="I49" t="n">
         <v>1836.237425323346</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.2</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>4.57</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>2.48</v>
       </c>
       <c r="N49" t="n">
-        <v>5.59</v>
+        <v>6.37</v>
       </c>
       <c r="O49" t="n">
         <v>-2.95</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>10.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1852.5</v>
+        <v>1809.5</v>
       </c>
       <c r="I50" t="n">
         <v>1844.889376145394</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.74</v>
+        <v>-5.98</v>
       </c>
       <c r="L50" t="n">
-        <v>4.31</v>
+        <v>6.96</v>
       </c>
       <c r="M50" t="n">
         <v>1.93</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.63</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1846.5</v>
+        <v>1921</v>
       </c>
       <c r="I51" t="n">
         <v>1919.187631809559</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.04</v>
+        <v>-6.16</v>
       </c>
       <c r="L51" t="n">
-        <v>3.04</v>
+        <v>6.19</v>
       </c>
       <c r="M51" t="n">
-        <v>0.97</v>
+        <v>1.44</v>
       </c>
       <c r="N51" t="n">
-        <v>4.67</v>
+        <v>5.04</v>
       </c>
       <c r="O51" t="n">
         <v>-6.75</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1881.5</v>
+        <v>1737.5</v>
       </c>
       <c r="I52" t="n">
         <v>1775.347244765932</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.06</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>5.21</v>
+        <v>9.92</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>4.41</v>
+        <v>7.81</v>
       </c>
       <c r="O52" t="n">
         <v>5.04</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>14.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1869.5</v>
+        <v>1965</v>
       </c>
       <c r="I53" t="n">
         <v>1882.639904379881</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.6</v>
+        <v>-13.09</v>
       </c>
       <c r="L53" t="n">
-        <v>8.859999999999999</v>
+        <v>13.09</v>
       </c>
       <c r="M53" t="n">
         <v>1.57</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>12.5</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1831.5</v>
+        <v>1728</v>
       </c>
       <c r="I54" t="n">
         <v>1787.462632843806</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.79</v>
+        <v>-12.06</v>
       </c>
       <c r="L54" t="n">
-        <v>6.87</v>
+        <v>12.62</v>
       </c>
       <c r="M54" t="n">
         <v>1.64</v>
       </c>
       <c r="N54" t="n">
-        <v>3.26</v>
+        <v>6.36</v>
       </c>
       <c r="O54" t="n">
         <v>5.88</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.28</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1383.5</v>
+        <v>1455.5</v>
       </c>
       <c r="I55" t="n">
         <v>1445.18913615581</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>19.94</v>
+        <v>15.77</v>
       </c>
       <c r="L55" t="n">
         <v>6.57</v>
@@ -3576,7 +4235,7 @@
         <v>2.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4.57</v>
+        <v>5.64</v>
       </c>
       <c r="O55" t="n">
         <v>-6.36</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.55</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45799.38541666666</v>
+        <v>45799.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>2347</v>
+        <v>2338.5</v>
       </c>
       <c r="I56" t="n">
         <v>2339.383012789421</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>61.25</v>
+        <v>60.67</v>
       </c>
       <c r="L56" t="n">
         <v>4.84</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.72</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2468</v>
+        <v>2647.5</v>
       </c>
       <c r="I57" t="n">
         <v>2519.011299777975</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.54</v>
+        <v>-13.21</v>
       </c>
       <c r="L57" t="n">
-        <v>8.02</v>
+        <v>14.18</v>
       </c>
       <c r="M57" t="n">
         <v>1.27</v>
       </c>
       <c r="N57" t="n">
-        <v>4.73</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O57" t="n">
         <v>-4.1</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>10.67</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2872</v>
+        <v>2786.6</v>
       </c>
       <c r="I58" t="n">
         <v>2834.928296608332</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>8.48</v>
+        <v>5.25</v>
       </c>
       <c r="L58" t="n">
         <v>6.74</v>
       </c>
       <c r="M58" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="N58" t="n">
         <v>4.47</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>2790</v>
+        <v>2816</v>
       </c>
       <c r="I59" t="n">
         <v>2800.843428945979</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.12</v>
+        <v>-1.06</v>
       </c>
       <c r="L59" t="n">
         <v>2.83</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.75</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2825</v>
+        <v>2650.9</v>
       </c>
       <c r="I60" t="n">
         <v>2652.351569662411</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>0.32</v>
+        <v>-5.86</v>
       </c>
       <c r="L60" t="n">
-        <v>2.76</v>
+        <v>7.21</v>
       </c>
       <c r="M60" t="n">
-        <v>0.11</v>
+        <v>1.66</v>
       </c>
       <c r="N60" t="n">
-        <v>1.8</v>
+        <v>6.55</v>
       </c>
       <c r="O60" t="n">
         <v>1.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.17</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2225.5</v>
+        <v>2323</v>
       </c>
       <c r="I61" t="n">
         <v>2254.611455826055</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K61" t="n">
-        <v>16.05</v>
+        <v>12.37</v>
       </c>
       <c r="L61" t="n">
         <v>4.79</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2272</v>
+        <v>2176.6</v>
       </c>
       <c r="I62" t="n">
         <v>2205.992055810997</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.2</v>
+        <v>-6.3</v>
       </c>
       <c r="L62" t="n">
-        <v>4.13</v>
+        <v>6.59</v>
       </c>
       <c r="M62" t="n">
         <v>-0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.36</v>
+        <v>4.89</v>
       </c>
       <c r="O62" t="n">
         <v>4.43</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.25</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2097</v>
+        <v>2188.8</v>
       </c>
       <c r="I63" t="n">
         <v>2155.684537154743</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K63" t="n">
-        <v>3.66</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L63" t="n">
         <v>4.75</v>
@@ -4032,7 +4787,7 @@
         <v>1.11</v>
       </c>
       <c r="N63" t="n">
-        <v>2.54</v>
+        <v>5.7</v>
       </c>
       <c r="O63" t="n">
         <v>-4.89</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.82</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45994.38541666666</v>
+        <v>45994.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>2795.5</v>
+        <v>2759.1</v>
       </c>
       <c r="I64" t="n">
         <v>2788.318278812291</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>27.72</v>
+        <v>26.06</v>
       </c>
       <c r="L64" t="n">
         <v>3.97</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.38</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2702.5</v>
+        <v>2741.3</v>
       </c>
       <c r="I65" t="n">
         <v>2722.930307634517</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>2.05</v>
+        <v>0.65</v>
       </c>
       <c r="L65" t="n">
         <v>5.65</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>2720</v>
+        <v>2687.2</v>
       </c>
       <c r="I66" t="n">
         <v>2691.147007473493</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.78</v>
+        <v>-1.97</v>
       </c>
       <c r="L66" t="n">
         <v>3.59</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.62</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>2766.3</v>
+        <v>2818</v>
       </c>
       <c r="I67" t="n">
         <v>2813.26026060128</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.94</v>
+        <v>-4.87</v>
       </c>
       <c r="L67" t="n">
-        <v>3.25</v>
+        <v>5.31</v>
       </c>
       <c r="M67" t="n">
         <v>1.81</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.95</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>2775.8</v>
+        <v>2594.7</v>
       </c>
       <c r="I68" t="n">
         <v>2687.481417547537</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.5</v>
+        <v>-7.92</v>
       </c>
       <c r="L68" t="n">
-        <v>1.98</v>
+        <v>15.64</v>
       </c>
       <c r="M68" t="n">
         <v>0.42</v>
       </c>
       <c r="N68" t="n">
-        <v>3.32</v>
+        <v>7.41</v>
       </c>
       <c r="O68" t="n">
         <v>1.78</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>10.95</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>2706</v>
+        <v>2857</v>
       </c>
       <c r="I69" t="n">
         <v>2849.902461947061</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.29</v>
+        <v>-10.11</v>
       </c>
       <c r="L69" t="n">
-        <v>7.91</v>
+        <v>12.89</v>
       </c>
       <c r="M69" t="n">
-        <v>0.87</v>
+        <v>5.32</v>
       </c>
       <c r="N69" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O69" t="n">
         <v>-7.41</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>11.52</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46066.55208333334</v>
+        <v>46069.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>3023.9</v>
+        <v>2808.9</v>
       </c>
       <c r="I70" t="n">
         <v>2930.060518679808</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
-        <v>5.84</v>
+        <v>-1.68</v>
       </c>
       <c r="L70" t="n">
-        <v>2.21</v>
+        <v>4.57</v>
       </c>
       <c r="M70" t="n">
-        <v>1.21</v>
+        <v>7.07</v>
       </c>
       <c r="N70" t="n">
-        <v>3.64</v>
+        <v>7.47</v>
       </c>
       <c r="O70" t="n">
         <v>5.4</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46090.55208333334</v>
+        <v>46091.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>2766.8</v>
+        <v>2870</v>
       </c>
       <c r="I71" t="n">
         <v>2771.066633468979</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K71" t="n">
-        <v>1.5</v>
+        <v>-2.18</v>
       </c>
       <c r="L71" t="n">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="M71" t="n">
         <v>2.81</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46101.38541666666</v>
+        <v>46101.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>2821.9</v>
+        <v>2801.7</v>
       </c>
       <c r="I72" t="n">
         <v>2817.451719833023</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.68</v>
+        <v>-2.38</v>
       </c>
       <c r="L72" t="n">
         <v>3.24</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.49</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>2685</v>
+        <v>2893.9</v>
       </c>
       <c r="I73" t="n">
         <v>2886.981969600014</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>10</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>4.17</v>
+        <v>-3.29</v>
       </c>
       <c r="L73" t="n">
         <v>3.49</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>4.67</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>6.72</v>
       </c>
       <c r="O73" t="n">
         <v>-3.36</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.68</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>4249.9</v>
+        <v>4154</v>
       </c>
       <c r="I74" t="n">
         <v>4154.873612999239</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K74" t="n">
-        <v>46.86</v>
+        <v>43.54</v>
       </c>
       <c r="L74" t="n">
         <v>4.52</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.42</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46234.38541666666</v>
+        <v>46234.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>3617.8</v>
+        <v>3647</v>
       </c>
       <c r="I75" t="n">
         <v>3638.49766990468</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>12.91</v>
+        <v>12.21</v>
       </c>
       <c r="L75" t="n">
         <v>2.46</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.04</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46240.38541666666</v>
+        <v>46240.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>3479.3</v>
+        <v>3435</v>
       </c>
       <c r="I76" t="n">
         <v>3463.289888308187</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.6</v>
+        <v>-5.81</v>
       </c>
       <c r="L76" t="n">
-        <v>4.77</v>
+        <v>5.9</v>
       </c>
       <c r="M76" t="n">
         <v>0.11</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>6.3</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>3306.1</v>
+        <v>3400</v>
       </c>
       <c r="I77" t="n">
         <v>3364.0873164043</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="L77" t="n">
         <v>5.62</v>
       </c>
       <c r="M77" t="n">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="N77" t="n">
         <v>4.45</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>6.02</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>3287.9</v>
+        <v>3219</v>
       </c>
       <c r="I78" t="n">
         <v>3235.597758632782</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.3</v>
+        <v>-5.32</v>
       </c>
       <c r="L78" t="n">
-        <v>4.09</v>
+        <v>6.08</v>
       </c>
       <c r="M78" t="n">
         <v>2.74</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>6.68</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>3168.8</v>
+        <v>3293.6</v>
       </c>
       <c r="I79" t="n">
         <v>3221.882077521886</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K79" t="n">
-        <v>1.56</v>
+        <v>-2.32</v>
       </c>
       <c r="L79" t="n">
         <v>7.26</v>
       </c>
       <c r="M79" t="n">
-        <v>0.77</v>
+        <v>1.27</v>
       </c>
       <c r="N79" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="O79" t="n">
         <v>3.13</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -5004,6 +5963,12 @@
       <c r="Q80" t="n">
         <v>30</v>
       </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7106,7 +8071,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="6">
@@ -7116,7 +8081,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -7126,7 +8091,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>133.2</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -7136,7 +8101,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7146,7 +8111,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="10">
@@ -7156,7 +8121,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="11">
@@ -7166,7 +8131,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -7176,7 +8141,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7186,7 +8151,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.5</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="14">
@@ -7196,7 +8161,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.59</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -7206,7 +8171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.17</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="16">
@@ -7216,7 +8181,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.02</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="17">
@@ -7226,7 +8191,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.65000000000001</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -7236,7 +8201,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -7246,7 +8211,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.7</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="20">
@@ -7256,7 +8221,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.25</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="21">
@@ -7266,7 +8231,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.51</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="22">
@@ -7276,7 +8241,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -7286,7 +8251,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -7296,7 +8261,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="25">
@@ -7306,7 +8271,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.5</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="26">
@@ -7316,7 +8281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.02</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="27">
@@ -7326,7 +8291,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -7336,7 +8301,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
